--- a/diseases/d098/2026-2029.xlsx
+++ b/diseases/d098/2026-2029.xlsx
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O13" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3028,6 +3028,396 @@
         </is>
       </c>
       <c r="BC13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ehrlichiosis-and-anaplasmosis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>埃立克体病和无形体病</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>43</v>
+      </c>
+      <c r="O14" t="n">
+        <v>43</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ehrlichiosis-and-anaplasmosis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>埃立克体病和无形体病</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>43</v>
+      </c>
+      <c r="O15" t="n">
+        <v>43</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Ontario IDTO reports anaplasmosis separately within the combined Ehrlichiosis and Anaplasmosis concept.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -3066,7 +3456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3539,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3159,7 +3549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -3179,7 +3569,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3211,7 +3601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>106</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d098/2026-2029.xlsx
+++ b/diseases/d098/2026-2029.xlsx
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="O12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="O13" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3418,6 +3418,396 @@
         </is>
       </c>
       <c r="BC15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ehrlichiosis-and-anaplasmosis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>埃立克体病和无形体病</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>15</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ehrlichiosis-and-anaplasmosis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D098</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ehrlichiosis and Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>埃立克体病和无形体病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>15</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Anaplasmosis</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Ontario IDTO reports anaplasmosis separately within the combined Ehrlichiosis and Anaplasmosis concept.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ANAPLASMOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -3456,7 +3846,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3929,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3549,7 +3939,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -3569,7 +3959,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -3601,7 +3991,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d098/2026-2029.xlsx
+++ b/diseases/d098/2026-2029.xlsx
@@ -765,11 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -782,23 +777,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -912,11 +897,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -929,23 +909,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1059,11 +1029,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1076,23 +1041,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1206,11 +1161,6 @@
       <c r="O5" t="n">
         <v>8</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1223,23 +1173,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1353,11 +1293,6 @@
       <c r="O6" t="n">
         <v>31</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1370,23 +1305,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1500,11 +1425,6 @@
       <c r="O7" t="n">
         <v>77</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1517,23 +1437,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1647,11 +1557,6 @@
       <c r="O8" t="n">
         <v>44</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1664,23 +1569,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1794,11 +1689,6 @@
       <c r="O9" t="n">
         <v>15</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1811,22 +1701,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>

--- a/diseases/d098/2026-2029.xlsx
+++ b/diseases/d098/2026-2029.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -777,13 +782,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -897,6 +912,11 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -909,13 +929,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1029,6 +1059,11 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1041,13 +1076,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1161,6 +1206,11 @@
       <c r="O5" t="n">
         <v>8</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1173,13 +1223,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1293,6 +1353,11 @@
       <c r="O6" t="n">
         <v>31</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1305,13 +1370,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1425,6 +1500,11 @@
       <c r="O7" t="n">
         <v>77</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1437,13 +1517,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1557,6 +1647,11 @@
       <c r="O8" t="n">
         <v>44</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1569,13 +1664,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1689,6 +1794,11 @@
       <c r="O9" t="n">
         <v>15</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1701,12 +1811,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
